--- a/estimation/notsensor/DenseModel/Dense_1st_torch_optimized/IWALQQ_1st_correction/angle/3_fold/13.xlsx
+++ b/estimation/notsensor/DenseModel/Dense_1st_torch_optimized/IWALQQ_1st_correction/angle/3_fold/13.xlsx
@@ -426,13 +426,13 @@
         <v>-22.3098112186618</v>
       </c>
       <c r="E2">
-        <v>-53.54632031522969</v>
+        <v>-35.03437368351104</v>
       </c>
       <c r="F2">
-        <v>-9.797719632177438</v>
+        <v>-6.15855744247223</v>
       </c>
       <c r="G2">
-        <v>-32.99014031061077</v>
+        <v>-20.78840633724479</v>
       </c>
     </row>
     <row r="3" spans="1:7">
@@ -449,13 +449,13 @@
         <v>-21.58785101019741</v>
       </c>
       <c r="E3">
-        <v>-53.42368244639096</v>
+        <v>-36.02958283075473</v>
       </c>
       <c r="F3">
-        <v>-9.564346114220958</v>
+        <v>-5.751139989416418</v>
       </c>
       <c r="G3">
-        <v>-33.37871311037357</v>
+        <v>-22.38918918257675</v>
       </c>
     </row>
     <row r="4" spans="1:7">
@@ -472,13 +472,13 @@
         <v>-20.7661902999863</v>
       </c>
       <c r="E4">
-        <v>-53.58788038543508</v>
+        <v>-38.10228123372448</v>
       </c>
       <c r="F4">
-        <v>-9.494203977189384</v>
+        <v>-6.39115355878747</v>
       </c>
       <c r="G4">
-        <v>-33.01859858770273</v>
+        <v>-22.30525857679238</v>
       </c>
     </row>
     <row r="5" spans="1:7">
@@ -495,13 +495,13 @@
         <v>-19.90718506617447</v>
       </c>
       <c r="E5">
-        <v>-53.14210532894953</v>
+        <v>-34.31628223892973</v>
       </c>
       <c r="F5">
-        <v>-9.691897194760733</v>
+        <v>-6.166911887102652</v>
       </c>
       <c r="G5">
-        <v>-33.26834697082173</v>
+        <v>-21.85209455064924</v>
       </c>
     </row>
     <row r="6" spans="1:7">
@@ -518,13 +518,13 @@
         <v>-19.02686702927876</v>
       </c>
       <c r="E6">
-        <v>-53.44692144287983</v>
+        <v>-35.15303328793402</v>
       </c>
       <c r="F6">
-        <v>-9.591596743944685</v>
+        <v>-6.200721632838411</v>
       </c>
       <c r="G6">
-        <v>-32.9351455281124</v>
+        <v>-20.58304657635272</v>
       </c>
     </row>
     <row r="7" spans="1:7">
@@ -541,13 +541,13 @@
         <v>-18.15982621261146</v>
       </c>
       <c r="E7">
-        <v>-53.79605207133068</v>
+        <v>-35.0685387556619</v>
       </c>
       <c r="F7">
-        <v>-9.564986921226993</v>
+        <v>-5.607120149025228</v>
       </c>
       <c r="G7">
-        <v>-33.02059898484484</v>
+        <v>-20.53028972263889</v>
       </c>
     </row>
     <row r="8" spans="1:7">
@@ -564,13 +564,13 @@
         <v>-17.315957321395</v>
       </c>
       <c r="E8">
-        <v>-54.12033383078295</v>
+        <v>-38.77606156014073</v>
       </c>
       <c r="F8">
-        <v>-9.700956784450003</v>
+        <v>-5.363785318823872</v>
       </c>
       <c r="G8">
-        <v>-32.93812088091582</v>
+        <v>-20.21983007251158</v>
       </c>
     </row>
     <row r="9" spans="1:7">
@@ -587,13 +587,13 @@
         <v>-16.54234613808189</v>
       </c>
       <c r="E9">
-        <v>-53.65051370943517</v>
+        <v>-34.94860438580576</v>
       </c>
       <c r="F9">
-        <v>-9.649469713286109</v>
+        <v>-6.524051824387486</v>
       </c>
       <c r="G9">
-        <v>-33.00393121569099</v>
+        <v>-21.46073675445153</v>
       </c>
     </row>
     <row r="10" spans="1:7">
@@ -610,13 +610,13 @@
         <v>-15.86135035657544</v>
       </c>
       <c r="E10">
-        <v>-54.13369056486858</v>
+        <v>-36.90490968559337</v>
       </c>
       <c r="F10">
-        <v>-9.62134467993382</v>
+        <v>-5.784449284082898</v>
       </c>
       <c r="G10">
-        <v>-32.94286406503721</v>
+        <v>-20.47643707835157</v>
       </c>
     </row>
     <row r="11" spans="1:7">
@@ -633,13 +633,13 @@
         <v>-15.29003853868885</v>
       </c>
       <c r="E11">
-        <v>-53.91291953216513</v>
+        <v>-36.1750962860432</v>
       </c>
       <c r="F11">
-        <v>-9.60590196355237</v>
+        <v>-6.15389026113943</v>
       </c>
       <c r="G11">
-        <v>-32.85571312607951</v>
+        <v>-20.11538070547481</v>
       </c>
     </row>
     <row r="12" spans="1:7">
@@ -656,13 +656,13 @@
         <v>-14.83498730438725</v>
       </c>
       <c r="E12">
-        <v>-53.92107078537894</v>
+        <v>-39.07045765537939</v>
       </c>
       <c r="F12">
-        <v>-9.56717540483889</v>
+        <v>-5.951739307342598</v>
       </c>
       <c r="G12">
-        <v>-32.58700773156625</v>
+        <v>-20.94657592674732</v>
       </c>
     </row>
     <row r="13" spans="1:7">
@@ -679,13 +679,13 @@
         <v>-14.4799766397806</v>
       </c>
       <c r="E13">
-        <v>-54.01407432031147</v>
+        <v>-38.03881693474398</v>
       </c>
       <c r="F13">
-        <v>-9.512843205997909</v>
+        <v>-6.069503679214676</v>
       </c>
       <c r="G13">
-        <v>-32.60105685919854</v>
+        <v>-20.99423454033067</v>
       </c>
     </row>
     <row r="14" spans="1:7">
@@ -702,13 +702,13 @@
         <v>-14.23246587488803</v>
       </c>
       <c r="E14">
-        <v>-54.46283137693108</v>
+        <v>-39.83157639574457</v>
       </c>
       <c r="F14">
-        <v>-9.505364352775485</v>
+        <v>-5.169695824063107</v>
       </c>
       <c r="G14">
-        <v>-32.2650861451456</v>
+        <v>-20.41907194524708</v>
       </c>
     </row>
     <row r="15" spans="1:7">
@@ -725,13 +725,13 @@
         <v>-14.07820385824111</v>
       </c>
       <c r="E15">
-        <v>-54.70345410756565</v>
+        <v>-39.95261797749559</v>
       </c>
       <c r="F15">
-        <v>-9.575637145545084</v>
+        <v>-6.325143904378995</v>
       </c>
       <c r="G15">
-        <v>-32.21491234458879</v>
+        <v>-19.32866762934071</v>
       </c>
     </row>
     <row r="16" spans="1:7">
@@ -748,13 +748,13 @@
         <v>-13.99696944289617</v>
       </c>
       <c r="E16">
-        <v>-54.79435529844012</v>
+        <v>-39.73832153050461</v>
       </c>
       <c r="F16">
-        <v>-9.612466820498346</v>
+        <v>-5.404671854442772</v>
       </c>
       <c r="G16">
-        <v>-32.12771505799354</v>
+        <v>-18.55783855070404</v>
       </c>
     </row>
     <row r="17" spans="1:7">
@@ -771,13 +771,13 @@
         <v>-13.96687000726199</v>
       </c>
       <c r="E17">
-        <v>-55.63015989637681</v>
+        <v>-40.87424847906266</v>
       </c>
       <c r="F17">
-        <v>-9.572397081205333</v>
+        <v>-4.901416833840622</v>
       </c>
       <c r="G17">
-        <v>-31.92514939753662</v>
+        <v>-19.39532380850116</v>
       </c>
     </row>
     <row r="18" spans="1:7">
@@ -794,13 +794,13 @@
         <v>-13.95439268090047</v>
       </c>
       <c r="E18">
-        <v>-55.64809718192119</v>
+        <v>-40.43539859145333</v>
       </c>
       <c r="F18">
-        <v>-9.447200773398578</v>
+        <v>-5.307307198467471</v>
       </c>
       <c r="G18">
-        <v>-31.94269363362199</v>
+        <v>-18.46666612655251</v>
       </c>
     </row>
     <row r="19" spans="1:7">
@@ -817,13 +817,13 @@
         <v>-13.95393688869952</v>
       </c>
       <c r="E19">
-        <v>-56.07252727617159</v>
+        <v>-38.7553777551107</v>
       </c>
       <c r="F19">
-        <v>-9.592546571567469</v>
+        <v>-5.11759823426881</v>
       </c>
       <c r="G19">
-        <v>-31.83082285112255</v>
+        <v>-17.39538021113543</v>
       </c>
     </row>
     <row r="20" spans="1:7">
@@ -840,13 +840,13 @@
         <v>-13.95273644947782</v>
       </c>
       <c r="E20">
-        <v>-55.75680659683083</v>
+        <v>-40.04335274695028</v>
       </c>
       <c r="F20">
-        <v>-9.263656384475766</v>
+        <v>-5.512724941641375</v>
       </c>
       <c r="G20">
-        <v>-31.37397004961228</v>
+        <v>-18.28192940909733</v>
       </c>
     </row>
     <row r="21" spans="1:7">
@@ -863,13 +863,13 @@
         <v>-13.9389953549504</v>
       </c>
       <c r="E21">
-        <v>-55.24391842343309</v>
+        <v>-42.28107100699654</v>
       </c>
       <c r="F21">
-        <v>-9.271271634370155</v>
+        <v>-5.188079482329528</v>
       </c>
       <c r="G21">
-        <v>-31.64507890018704</v>
+        <v>-18.93912897791683</v>
       </c>
     </row>
     <row r="22" spans="1:7">
@@ -886,13 +886,13 @@
         <v>-13.90399592784824</v>
       </c>
       <c r="E22">
-        <v>-55.75479935072693</v>
+        <v>-39.42035246381904</v>
       </c>
       <c r="F22">
-        <v>-9.290429724829227</v>
+        <v>-4.135161314832145</v>
       </c>
       <c r="G22">
-        <v>-31.48491718990626</v>
+        <v>-18.61293430484136</v>
       </c>
     </row>
     <row r="23" spans="1:7">
@@ -909,13 +909,13 @@
         <v>-13.83188683138135</v>
       </c>
       <c r="E23">
-        <v>-56.24060498532179</v>
+        <v>-42.87118098341007</v>
       </c>
       <c r="F23">
-        <v>-9.249988210572566</v>
+        <v>-4.813634390506686</v>
       </c>
       <c r="G23">
-        <v>-31.44940331263373</v>
+        <v>-17.46431735617244</v>
       </c>
     </row>
     <row r="24" spans="1:7">
@@ -932,13 +932,13 @@
         <v>-13.72870594159409</v>
       </c>
       <c r="E24">
-        <v>-56.50689397451332</v>
+        <v>-40.58017616971555</v>
       </c>
       <c r="F24">
-        <v>-9.457676394139492</v>
+        <v>-4.601940420789895</v>
       </c>
       <c r="G24">
-        <v>-31.5768303486222</v>
+        <v>-18.01096125670798</v>
       </c>
     </row>
     <row r="25" spans="1:7">
@@ -955,13 +955,13 @@
         <v>-13.59549036571109</v>
       </c>
       <c r="E25">
-        <v>-56.09432961428152</v>
+        <v>-43.1132573542011</v>
       </c>
       <c r="F25">
-        <v>-8.98829704103183</v>
+        <v>-4.022381657328914</v>
       </c>
       <c r="G25">
-        <v>-31.31041254107658</v>
+        <v>-18.82139273635818</v>
       </c>
     </row>
     <row r="26" spans="1:7">
@@ -978,13 +978,13 @@
         <v>-13.43114391591625</v>
       </c>
       <c r="E26">
-        <v>-56.3755750210019</v>
+        <v>-42.58071107513607</v>
       </c>
       <c r="F26">
-        <v>-9.031817675514585</v>
+        <v>-4.092681571062314</v>
       </c>
       <c r="G26">
-        <v>-31.39478675996322</v>
+        <v>-20.11608254112913</v>
       </c>
     </row>
     <row r="27" spans="1:7">
@@ -1001,13 +1001,13 @@
         <v>-13.23464188863326</v>
       </c>
       <c r="E27">
-        <v>-56.49860007436828</v>
+        <v>-40.98395302613547</v>
       </c>
       <c r="F27">
-        <v>-8.954079886949323</v>
+        <v>-4.780073286599651</v>
       </c>
       <c r="G27">
-        <v>-31.45227934907097</v>
+        <v>-18.32517341020406</v>
       </c>
     </row>
     <row r="28" spans="1:7">
@@ -1024,13 +1024,13 @@
         <v>-12.99682347667484</v>
       </c>
       <c r="E28">
-        <v>-56.61990317549324</v>
+        <v>-43.72881509030073</v>
       </c>
       <c r="F28">
-        <v>-9.032136000403588</v>
+        <v>-4.206748781474797</v>
       </c>
       <c r="G28">
-        <v>-31.59805922189278</v>
+        <v>-19.02072895964155</v>
       </c>
     </row>
     <row r="29" spans="1:7">
@@ -1047,13 +1047,13 @@
         <v>-12.72579297747149</v>
       </c>
       <c r="E29">
-        <v>-56.01786633066201</v>
+        <v>-41.44655249567803</v>
       </c>
       <c r="F29">
-        <v>-9.025562037148598</v>
+        <v>-3.728124347122519</v>
       </c>
       <c r="G29">
-        <v>-31.73666928071291</v>
+        <v>-19.27139188096578</v>
       </c>
     </row>
     <row r="30" spans="1:7">
@@ -1070,13 +1070,13 @@
         <v>-12.42621098307399</v>
       </c>
       <c r="E30">
-        <v>-56.14985096985257</v>
+        <v>-41.51703592937042</v>
       </c>
       <c r="F30">
-        <v>-9.01588361437287</v>
+        <v>-4.376684385466239</v>
       </c>
       <c r="G30">
-        <v>-31.26470052827032</v>
+        <v>-18.6499197196061</v>
       </c>
     </row>
     <row r="31" spans="1:7">
@@ -1093,13 +1093,13 @@
         <v>-12.1008296266751</v>
       </c>
       <c r="E31">
-        <v>-55.82289967497277</v>
+        <v>-42.6459052511875</v>
       </c>
       <c r="F31">
-        <v>-9.052568578198109</v>
+        <v>-3.715706509039558</v>
       </c>
       <c r="G31">
-        <v>-31.63904543094172</v>
+        <v>-18.80495256721017</v>
       </c>
     </row>
     <row r="32" spans="1:7">
@@ -1116,13 +1116,13 @@
         <v>-11.75371032084772</v>
       </c>
       <c r="E32">
-        <v>-56.57442710738972</v>
+        <v>-42.16784557138276</v>
       </c>
       <c r="F32">
-        <v>-9.115712516752595</v>
+        <v>-4.683389624167988</v>
       </c>
       <c r="G32">
-        <v>-31.5243830309163</v>
+        <v>-19.0524804019087</v>
       </c>
     </row>
     <row r="33" spans="1:7">
@@ -1139,13 +1139,13 @@
         <v>-11.38280309565323</v>
       </c>
       <c r="E33">
-        <v>-56.31696751039463</v>
+        <v>-42.00839120886167</v>
       </c>
       <c r="F33">
-        <v>-9.077963302552181</v>
+        <v>-4.07902131568869</v>
       </c>
       <c r="G33">
-        <v>-31.56064178093516</v>
+        <v>-18.66429741888315</v>
       </c>
     </row>
     <row r="34" spans="1:7">
@@ -1162,13 +1162,13 @@
         <v>-11.00174880237991</v>
       </c>
       <c r="E34">
-        <v>-55.9338472881607</v>
+        <v>-41.48503773203221</v>
       </c>
       <c r="F34">
-        <v>-8.812618523464526</v>
+        <v>-4.054792198888382</v>
       </c>
       <c r="G34">
-        <v>-32.05931008315197</v>
+        <v>-20.3814889770125</v>
       </c>
     </row>
     <row r="35" spans="1:7">
@@ -1185,13 +1185,13 @@
         <v>-10.62219463415551</v>
       </c>
       <c r="E35">
-        <v>-55.41573212363961</v>
+        <v>-39.93204512007875</v>
       </c>
       <c r="F35">
-        <v>-9.151212076700128</v>
+        <v>-3.802756488387602</v>
       </c>
       <c r="G35">
-        <v>-31.72093343012837</v>
+        <v>-17.97569898089644</v>
       </c>
     </row>
     <row r="36" spans="1:7">
@@ -1208,13 +1208,13 @@
         <v>-10.25250253339907</v>
       </c>
       <c r="E36">
-        <v>-56.12640705991485</v>
+        <v>-41.98610205979592</v>
       </c>
       <c r="F36">
-        <v>-9.020821213490731</v>
+        <v>-5.239278319016812</v>
       </c>
       <c r="G36">
-        <v>-31.54374475650272</v>
+        <v>-19.16537993643447</v>
       </c>
     </row>
     <row r="37" spans="1:7">
@@ -1231,13 +1231,13 @@
         <v>-9.900524906369061</v>
       </c>
       <c r="E37">
-        <v>-55.88213664346711</v>
+        <v>-40.19912319586612</v>
       </c>
       <c r="F37">
-        <v>-9.05944384150351</v>
+        <v>-3.691475808533334</v>
       </c>
       <c r="G37">
-        <v>-31.76858045680233</v>
+        <v>-18.85264925206721</v>
       </c>
     </row>
     <row r="38" spans="1:7">
@@ -1254,13 +1254,13 @@
         <v>-9.566869183990436</v>
       </c>
       <c r="E38">
-        <v>-55.34024585828725</v>
+        <v>-41.17517463382037</v>
       </c>
       <c r="F38">
-        <v>-9.113112071639444</v>
+        <v>-3.496441633194008</v>
       </c>
       <c r="G38">
-        <v>-31.69098954572566</v>
+        <v>-18.84183866560872</v>
       </c>
     </row>
     <row r="39" spans="1:7">
@@ -1277,13 +1277,13 @@
         <v>-9.26327473341957</v>
       </c>
       <c r="E39">
-        <v>-55.60356982912227</v>
+        <v>-39.35905503965121</v>
       </c>
       <c r="F39">
-        <v>-9.105174141664781</v>
+        <v>-4.665439901322397</v>
       </c>
       <c r="G39">
-        <v>-31.75060502216047</v>
+        <v>-19.8643950059605</v>
       </c>
     </row>
     <row r="40" spans="1:7">
@@ -1300,13 +1300,13 @@
         <v>-8.999366717951448</v>
       </c>
       <c r="E40">
-        <v>-55.7430377716105</v>
+        <v>-41.3232036564201</v>
       </c>
       <c r="F40">
-        <v>-9.070951840538051</v>
+        <v>-4.579356774435729</v>
       </c>
       <c r="G40">
-        <v>-32.17202008894561</v>
+        <v>-19.76397953866332</v>
       </c>
     </row>
     <row r="41" spans="1:7">
@@ -1323,13 +1323,13 @@
         <v>-8.779666812714986</v>
       </c>
       <c r="E41">
-        <v>-55.34631401345753</v>
+        <v>-38.62011450073859</v>
       </c>
       <c r="F41">
-        <v>-8.972178478150965</v>
+        <v>-4.332414262159002</v>
       </c>
       <c r="G41">
-        <v>-31.95157086148554</v>
+        <v>-18.90562294651386</v>
       </c>
     </row>
     <row r="42" spans="1:7">
@@ -1346,13 +1346,13 @@
         <v>-8.606758848757849</v>
       </c>
       <c r="E42">
-        <v>-55.12131451814943</v>
+        <v>-39.99198853051828</v>
       </c>
       <c r="F42">
-        <v>-9.019644519995559</v>
+        <v>-4.43930570106863</v>
       </c>
       <c r="G42">
-        <v>-31.77374739075274</v>
+        <v>-18.95135978841166</v>
       </c>
     </row>
     <row r="43" spans="1:7">
@@ -1369,13 +1369,13 @@
         <v>-8.475512709341764</v>
       </c>
       <c r="E43">
-        <v>-54.78374621595865</v>
+        <v>-39.33991091578378</v>
       </c>
       <c r="F43">
-        <v>-9.023305256219098</v>
+        <v>-4.407460542520973</v>
       </c>
       <c r="G43">
-        <v>-31.72981231326469</v>
+        <v>-17.44239823415693</v>
       </c>
     </row>
     <row r="44" spans="1:7">
@@ -1392,13 +1392,13 @@
         <v>-8.38851000650444</v>
       </c>
       <c r="E44">
-        <v>-54.55947127649177</v>
+        <v>-39.16724473034532</v>
       </c>
       <c r="F44">
-        <v>-9.077557477911348</v>
+        <v>-4.494227830363112</v>
       </c>
       <c r="G44">
-        <v>-31.89052936755969</v>
+        <v>-18.5696207822783</v>
       </c>
     </row>
     <row r="45" spans="1:7">
@@ -1415,13 +1415,13 @@
         <v>-8.348098794458917</v>
       </c>
       <c r="E45">
-        <v>-54.95686977727188</v>
+        <v>-40.49493443923217</v>
       </c>
       <c r="F45">
-        <v>-9.035988760969373</v>
+        <v>-3.827425083579445</v>
       </c>
       <c r="G45">
-        <v>-31.77593979953613</v>
+        <v>-18.84855741778068</v>
       </c>
     </row>
     <row r="46" spans="1:7">
@@ -1438,13 +1438,13 @@
         <v>-8.351496657128777</v>
       </c>
       <c r="E46">
-        <v>-54.45938520821124</v>
+        <v>-39.51113704648781</v>
       </c>
       <c r="F46">
-        <v>-8.955494136331811</v>
+        <v>-3.761680699911807</v>
       </c>
       <c r="G46">
-        <v>-31.83420043520899</v>
+        <v>-18.49479748727246</v>
       </c>
     </row>
     <row r="47" spans="1:7">
@@ -1461,13 +1461,13 @@
         <v>-8.39492923550959</v>
       </c>
       <c r="E47">
-        <v>-54.39799268608926</v>
+        <v>-38.2060829149283</v>
       </c>
       <c r="F47">
-        <v>-9.047031150464775</v>
+        <v>-4.479748007178249</v>
       </c>
       <c r="G47">
-        <v>-31.86245925193221</v>
+        <v>-20.05200031112546</v>
       </c>
     </row>
     <row r="48" spans="1:7">
@@ -1484,13 +1484,13 @@
         <v>-8.468451864155977</v>
       </c>
       <c r="E48">
-        <v>-54.2562084291461</v>
+        <v>-36.72897847039537</v>
       </c>
       <c r="F48">
-        <v>-9.153344140788787</v>
+        <v>-4.060476119418895</v>
       </c>
       <c r="G48">
-        <v>-31.32269466502728</v>
+        <v>-18.51527983252394</v>
       </c>
     </row>
     <row r="49" spans="1:7">
@@ -1507,13 +1507,13 @@
         <v>-8.568104956115667</v>
       </c>
       <c r="E49">
-        <v>-54.12015042758565</v>
+        <v>-38.02551680658345</v>
       </c>
       <c r="F49">
-        <v>-9.116513476019328</v>
+        <v>-4.394461484367047</v>
       </c>
       <c r="G49">
-        <v>-31.93664857746728</v>
+        <v>-19.37286506756275</v>
       </c>
     </row>
     <row r="50" spans="1:7">
@@ -1530,13 +1530,13 @@
         <v>-8.692744798738257</v>
       </c>
       <c r="E50">
-        <v>-54.26720809251074</v>
+        <v>-36.5847646871471</v>
       </c>
       <c r="F50">
-        <v>-9.093192614561525</v>
+        <v>-4.631836037355646</v>
       </c>
       <c r="G50">
-        <v>-32.24237911329174</v>
+        <v>-18.67170973034558</v>
       </c>
     </row>
     <row r="51" spans="1:7">
@@ -1553,13 +1553,13 @@
         <v>-8.836327755746556</v>
       </c>
       <c r="E51">
-        <v>-53.48645728520379</v>
+        <v>-38.00125550708736</v>
       </c>
       <c r="F51">
-        <v>-9.087147609082292</v>
+        <v>-3.763212143532037</v>
       </c>
       <c r="G51">
-        <v>-32.10505768432277</v>
+        <v>-19.66096860366336</v>
       </c>
     </row>
     <row r="52" spans="1:7">
@@ -1576,13 +1576,13 @@
         <v>-8.992353175158611</v>
       </c>
       <c r="E52">
-        <v>-53.75648905816267</v>
+        <v>-37.12151565432826</v>
       </c>
       <c r="F52">
-        <v>-8.843136140528566</v>
+        <v>-3.759239417243157</v>
       </c>
       <c r="G52">
-        <v>-31.83896099969446</v>
+        <v>-20.7356693468042</v>
       </c>
     </row>
     <row r="53" spans="1:7">
@@ -1599,13 +1599,13 @@
         <v>-9.149912426461132</v>
       </c>
       <c r="E53">
-        <v>-53.59561275480318</v>
+        <v>-35.18133625048196</v>
       </c>
       <c r="F53">
-        <v>-9.222629690883348</v>
+        <v>-4.142451113160913</v>
       </c>
       <c r="G53">
-        <v>-32.09611755609397</v>
+        <v>-18.76687798296301</v>
       </c>
     </row>
     <row r="54" spans="1:7">
@@ -1622,13 +1622,13 @@
         <v>-9.302939322541164</v>
       </c>
       <c r="E54">
-        <v>-53.47621274487994</v>
+        <v>-35.5551889506592</v>
       </c>
       <c r="F54">
-        <v>-9.182945188054267</v>
+        <v>-4.135592874694103</v>
       </c>
       <c r="G54">
-        <v>-32.13745799351562</v>
+        <v>-19.01260322561541</v>
       </c>
     </row>
     <row r="55" spans="1:7">
@@ -1645,13 +1645,13 @@
         <v>-9.451350809761271</v>
       </c>
       <c r="E55">
-        <v>-53.11089395397016</v>
+        <v>-35.78755400894078</v>
       </c>
       <c r="F55">
-        <v>-9.222155766888154</v>
+        <v>-4.828853804354059</v>
       </c>
       <c r="G55">
-        <v>-31.78771375474654</v>
+        <v>-19.68841799200223</v>
       </c>
     </row>
     <row r="56" spans="1:7">
@@ -1668,13 +1668,13 @@
         <v>-9.591047286136426</v>
       </c>
       <c r="E56">
-        <v>-53.67371987448748</v>
+        <v>-35.39822298460533</v>
       </c>
       <c r="F56">
-        <v>-9.022197453931248</v>
+        <v>-4.483232160192216</v>
       </c>
       <c r="G56">
-        <v>-31.69952247685313</v>
+        <v>-19.57839201100455</v>
       </c>
     </row>
     <row r="57" spans="1:7">
@@ -1691,13 +1691,13 @@
         <v>-9.71837736354299</v>
       </c>
       <c r="E57">
-        <v>-52.78668351798351</v>
+        <v>-36.23610841634854</v>
       </c>
       <c r="F57">
-        <v>-9.337099162598355</v>
+        <v>-4.621106429778544</v>
       </c>
       <c r="G57">
-        <v>-31.93097264714019</v>
+        <v>-19.29352122262304</v>
       </c>
     </row>
     <row r="58" spans="1:7">
@@ -1714,13 +1714,13 @@
         <v>-9.826213108202117</v>
       </c>
       <c r="E58">
-        <v>-52.94169431538457</v>
+        <v>-36.37272342021194</v>
       </c>
       <c r="F58">
-        <v>-9.273120611026432</v>
+        <v>-4.444966657863368</v>
       </c>
       <c r="G58">
-        <v>-32.12726151325467</v>
+        <v>-19.77052614246723</v>
       </c>
     </row>
     <row r="59" spans="1:7">
@@ -1737,13 +1737,13 @@
         <v>-9.911277976068734</v>
       </c>
       <c r="E59">
-        <v>-52.68884017645529</v>
+        <v>-36.81602479777081</v>
       </c>
       <c r="F59">
-        <v>-9.24463211716655</v>
+        <v>-5.750177096219831</v>
       </c>
       <c r="G59">
-        <v>-32.48632990353509</v>
+        <v>-18.03209577943069</v>
       </c>
     </row>
     <row r="60" spans="1:7">
@@ -1760,13 +1760,13 @@
         <v>-9.977831545046463</v>
       </c>
       <c r="E60">
-        <v>-52.85522763268211</v>
+        <v>-34.17141409118735</v>
       </c>
       <c r="F60">
-        <v>-9.181012670910953</v>
+        <v>-5.29106946171647</v>
       </c>
       <c r="G60">
-        <v>-32.32379784264819</v>
+        <v>-18.49830004445301</v>
       </c>
     </row>
     <row r="61" spans="1:7">
@@ -1783,13 +1783,13 @@
         <v>-10.02571832808909</v>
       </c>
       <c r="E61">
-        <v>-52.05691653529193</v>
+        <v>-35.60725734479939</v>
       </c>
       <c r="F61">
-        <v>-9.510131505544198</v>
+        <v>-5.248215963350594</v>
       </c>
       <c r="G61">
-        <v>-32.35225943028569</v>
+        <v>-18.50658965048335</v>
       </c>
     </row>
     <row r="62" spans="1:7">
@@ -1806,13 +1806,13 @@
         <v>-10.0554262086952</v>
       </c>
       <c r="E62">
-        <v>-52.61412828015823</v>
+        <v>-34.47997072464798</v>
       </c>
       <c r="F62">
-        <v>-9.590270390240505</v>
+        <v>-4.808520604105732</v>
       </c>
       <c r="G62">
-        <v>-32.00466290793522</v>
+        <v>-19.8080875921558</v>
       </c>
     </row>
     <row r="63" spans="1:7">
@@ -1829,13 +1829,13 @@
         <v>-10.06417890490873</v>
       </c>
       <c r="E63">
-        <v>-52.41418143517907</v>
+        <v>-35.73830006139635</v>
       </c>
       <c r="F63">
-        <v>-9.334974621112792</v>
+        <v>-4.959409768905141</v>
       </c>
       <c r="G63">
-        <v>-32.4747562363298</v>
+        <v>-18.7284624125253</v>
       </c>
     </row>
     <row r="64" spans="1:7">
@@ -1852,13 +1852,13 @@
         <v>-10.05161725544968</v>
       </c>
       <c r="E64">
-        <v>-52.1624050730636</v>
+        <v>-35.41079855692463</v>
       </c>
       <c r="F64">
-        <v>-9.255364892155482</v>
+        <v>-4.797157514162454</v>
       </c>
       <c r="G64">
-        <v>-32.5241893023222</v>
+        <v>-20.43678005333664</v>
       </c>
     </row>
     <row r="65" spans="1:7">
@@ -1875,13 +1875,13 @@
         <v>-10.02578652499947</v>
       </c>
       <c r="E65">
-        <v>-52.26700602992978</v>
+        <v>-33.02606565245635</v>
       </c>
       <c r="F65">
-        <v>-9.467156457749311</v>
+        <v>-4.6565212614596</v>
       </c>
       <c r="G65">
-        <v>-32.08225961246658</v>
+        <v>-19.11618026390259</v>
       </c>
     </row>
     <row r="66" spans="1:7">
@@ -1898,13 +1898,13 @@
         <v>-9.989150043678942</v>
       </c>
       <c r="E66">
-        <v>-52.53345577994859</v>
+        <v>-33.28759861182134</v>
       </c>
       <c r="F66">
-        <v>-9.198631003293738</v>
+        <v>-4.754730032687831</v>
       </c>
       <c r="G66">
-        <v>-32.35780707697312</v>
+        <v>-19.10929763972644</v>
       </c>
     </row>
     <row r="67" spans="1:7">
@@ -1921,13 +1921,13 @@
         <v>-9.943916447981518</v>
       </c>
       <c r="E67">
-        <v>-52.21375343983658</v>
+        <v>-34.59328220126792</v>
       </c>
       <c r="F67">
-        <v>-9.407277526902744</v>
+        <v>-5.244179096972139</v>
       </c>
       <c r="G67">
-        <v>-32.32449885066613</v>
+        <v>-20.09699393554969</v>
       </c>
     </row>
     <row r="68" spans="1:7">
@@ -1944,13 +1944,13 @@
         <v>-9.888689712182288</v>
       </c>
       <c r="E68">
-        <v>-52.09654747557006</v>
+        <v>-33.60242265330859</v>
       </c>
       <c r="F68">
-        <v>-9.462338626391306</v>
+        <v>-5.770356676994361</v>
       </c>
       <c r="G68">
-        <v>-32.47378459121403</v>
+        <v>-18.63522586323004</v>
       </c>
     </row>
     <row r="69" spans="1:7">
@@ -1967,13 +1967,13 @@
         <v>-9.822714704144079</v>
       </c>
       <c r="E69">
-        <v>-52.25508595422309</v>
+        <v>-33.94655724281048</v>
       </c>
       <c r="F69">
-        <v>-9.413020242515366</v>
+        <v>-5.820934700962792</v>
       </c>
       <c r="G69">
-        <v>-32.26152896396366</v>
+        <v>-19.64471548033831</v>
       </c>
     </row>
     <row r="70" spans="1:7">
@@ -1990,13 +1990,13 @@
         <v>-9.754203808303403</v>
       </c>
       <c r="E70">
-        <v>-52.28322702382525</v>
+        <v>-33.39629330919045</v>
       </c>
       <c r="F70">
-        <v>-9.510115668485044</v>
+        <v>-5.489462677302443</v>
       </c>
       <c r="G70">
-        <v>-32.0753298130165</v>
+        <v>-17.91293765856293</v>
       </c>
     </row>
     <row r="71" spans="1:7">
@@ -2013,13 +2013,13 @@
         <v>-9.684877879350104</v>
       </c>
       <c r="E71">
-        <v>-52.61520492485356</v>
+        <v>-33.21687064053254</v>
       </c>
       <c r="F71">
-        <v>-9.556420260003902</v>
+        <v>-5.230419068125843</v>
       </c>
       <c r="G71">
-        <v>-32.20676095383472</v>
+        <v>-20.81538066229877</v>
       </c>
     </row>
     <row r="72" spans="1:7">
@@ -2036,13 +2036,13 @@
         <v>-9.615669812839364</v>
       </c>
       <c r="E72">
-        <v>-51.79008639345647</v>
+        <v>-33.61081844411881</v>
       </c>
       <c r="F72">
-        <v>-9.579995108297894</v>
+        <v>-5.623292161980737</v>
       </c>
       <c r="G72">
-        <v>-32.23272639013561</v>
+        <v>-18.81256185613218</v>
       </c>
     </row>
     <row r="73" spans="1:7">
@@ -2059,13 +2059,13 @@
         <v>-9.54405614325389</v>
       </c>
       <c r="E73">
-        <v>-52.30257379690453</v>
+        <v>-36.83028496242096</v>
       </c>
       <c r="F73">
-        <v>-9.514549055232077</v>
+        <v>-5.14568842609096</v>
       </c>
       <c r="G73">
-        <v>-32.38186894958893</v>
+        <v>-20.49509034719259</v>
       </c>
     </row>
     <row r="74" spans="1:7">
@@ -2082,13 +2082,13 @@
         <v>-9.46694524594724</v>
       </c>
       <c r="E74">
-        <v>-52.54429128613044</v>
+        <v>-35.2948922646983</v>
       </c>
       <c r="F74">
-        <v>-9.470004950801469</v>
+        <v>-5.717790310249094</v>
       </c>
       <c r="G74">
-        <v>-32.13033535478787</v>
+        <v>-17.64297756729029</v>
       </c>
     </row>
     <row r="75" spans="1:7">
@@ -2105,13 +2105,13 @@
         <v>-9.391045085115771</v>
       </c>
       <c r="E75">
-        <v>-52.22042048569437</v>
+        <v>-33.79092491235188</v>
       </c>
       <c r="F75">
-        <v>-9.645577162109198</v>
+        <v>-5.360628992934402</v>
       </c>
       <c r="G75">
-        <v>-32.33918774122387</v>
+        <v>-19.03182425301642</v>
       </c>
     </row>
     <row r="76" spans="1:7">
@@ -2128,13 +2128,13 @@
         <v>-9.315887095121271</v>
       </c>
       <c r="E76">
-        <v>-52.12955099413796</v>
+        <v>-34.38939671602057</v>
       </c>
       <c r="F76">
-        <v>-9.582084016400358</v>
+        <v>-5.41837566172907</v>
       </c>
       <c r="G76">
-        <v>-31.94371493692085</v>
+        <v>-18.63368811482705</v>
       </c>
     </row>
     <row r="77" spans="1:7">
@@ -2151,13 +2151,13 @@
         <v>-9.240358186405798</v>
       </c>
       <c r="E77">
-        <v>-52.90581068734779</v>
+        <v>-34.2319552601959</v>
       </c>
       <c r="F77">
-        <v>-9.486837171160477</v>
+        <v>-5.653928952914914</v>
       </c>
       <c r="G77">
-        <v>-32.24083805434321</v>
+        <v>-19.297164477989</v>
       </c>
     </row>
     <row r="78" spans="1:7">
@@ -2174,13 +2174,13 @@
         <v>-9.160518728962183</v>
       </c>
       <c r="E78">
-        <v>-52.3608314828947</v>
+        <v>-36.34869760136425</v>
       </c>
       <c r="F78">
-        <v>-9.619714056730636</v>
+        <v>-5.929368669434058</v>
       </c>
       <c r="G78">
-        <v>-31.90088475400653</v>
+        <v>-20.74657097326502</v>
       </c>
     </row>
     <row r="79" spans="1:7">
@@ -2197,13 +2197,13 @@
         <v>-9.071133572908494</v>
       </c>
       <c r="E79">
-        <v>-52.65030512688701</v>
+        <v>-35.88411692444334</v>
       </c>
       <c r="F79">
-        <v>-9.807651843826116</v>
+        <v>-6.067026763162928</v>
       </c>
       <c r="G79">
-        <v>-32.20082183513727</v>
+        <v>-18.61867479080645</v>
       </c>
     </row>
     <row r="80" spans="1:7">
@@ -2220,13 +2220,13 @@
         <v>-8.977708850833045</v>
       </c>
       <c r="E80">
-        <v>-52.89287283710787</v>
+        <v>-35.77086431798551</v>
       </c>
       <c r="F80">
-        <v>-9.603606183864702</v>
+        <v>-5.260808800937211</v>
       </c>
       <c r="G80">
-        <v>-31.78181105205002</v>
+        <v>-18.94955057527445</v>
       </c>
     </row>
     <row r="81" spans="1:7">
@@ -2243,13 +2243,13 @@
         <v>-8.878861963970987</v>
       </c>
       <c r="E81">
-        <v>-53.30737311997796</v>
+        <v>-37.46015946909585</v>
       </c>
       <c r="F81">
-        <v>-9.752090689194755</v>
+        <v>-5.217134942907137</v>
       </c>
       <c r="G81">
-        <v>-31.75675187759051</v>
+        <v>-18.59254796541052</v>
       </c>
     </row>
     <row r="82" spans="1:7">
@@ -2266,13 +2266,13 @@
         <v>-8.77285419728417</v>
       </c>
       <c r="E82">
-        <v>-53.01326458283879</v>
+        <v>-35.787685334687</v>
       </c>
       <c r="F82">
-        <v>-9.727318757191929</v>
+        <v>-6.269374492419753</v>
       </c>
       <c r="G82">
-        <v>-32.04384569730165</v>
+        <v>-18.91976559705763</v>
       </c>
     </row>
     <row r="83" spans="1:7">
@@ -2289,13 +2289,13 @@
         <v>-8.656089863938258</v>
       </c>
       <c r="E83">
-        <v>-53.78891179993909</v>
+        <v>-35.99054964904562</v>
       </c>
       <c r="F83">
-        <v>-9.798311938189812</v>
+        <v>-6.080632380682468</v>
       </c>
       <c r="G83">
-        <v>-32.05980500971009</v>
+        <v>-18.90296292317306</v>
       </c>
     </row>
     <row r="84" spans="1:7">
@@ -2312,13 +2312,13 @@
         <v>-8.52313072604942</v>
       </c>
       <c r="E84">
-        <v>-53.39462662503925</v>
+        <v>-35.63095032080752</v>
       </c>
       <c r="F84">
-        <v>-9.756562876736716</v>
+        <v>-5.322174237748658</v>
       </c>
       <c r="G84">
-        <v>-31.98971000137071</v>
+        <v>-19.39528077140915</v>
       </c>
     </row>
     <row r="85" spans="1:7">
@@ -2335,13 +2335,13 @@
         <v>-8.379315205980589</v>
       </c>
       <c r="E85">
-        <v>-54.43524164903935</v>
+        <v>-36.40881535805308</v>
       </c>
       <c r="F85">
-        <v>-9.659544062540698</v>
+        <v>-5.777537991467921</v>
       </c>
       <c r="G85">
-        <v>-31.79468079783394</v>
+        <v>-19.87715881428716</v>
       </c>
     </row>
     <row r="86" spans="1:7">
@@ -2358,13 +2358,13 @@
         <v>-8.223226457985476</v>
       </c>
       <c r="E86">
-        <v>-54.36455330189812</v>
+        <v>-38.5273147471364</v>
       </c>
       <c r="F86">
-        <v>-9.758115898350045</v>
+        <v>-6.103807145269573</v>
       </c>
       <c r="G86">
-        <v>-32.01938076576644</v>
+        <v>-19.83826321474626</v>
       </c>
     </row>
     <row r="87" spans="1:7">
@@ -2381,13 +2381,13 @@
         <v>-8.052960542780081</v>
       </c>
       <c r="E87">
-        <v>-55.15669208921584</v>
+        <v>-35.66768530195775</v>
       </c>
       <c r="F87">
-        <v>-9.685106263795328</v>
+        <v>-6.188714766440507</v>
       </c>
       <c r="G87">
-        <v>-31.63111832964794</v>
+        <v>-19.50405205564745</v>
       </c>
     </row>
     <row r="88" spans="1:7">
@@ -2404,13 +2404,13 @@
         <v>-7.865163730470276</v>
       </c>
       <c r="E88">
-        <v>-55.21336480930334</v>
+        <v>-39.94962692041352</v>
       </c>
       <c r="F88">
-        <v>-9.770832264998065</v>
+        <v>-5.543472591989632</v>
       </c>
       <c r="G88">
-        <v>-31.61943541443985</v>
+        <v>-17.89358255406758</v>
       </c>
     </row>
     <row r="89" spans="1:7">
@@ -2427,13 +2427,13 @@
         <v>-7.654607568476747</v>
       </c>
       <c r="E89">
-        <v>-55.2465177675135</v>
+        <v>-38.78899035343263</v>
       </c>
       <c r="F89">
-        <v>-9.783361754348064</v>
+        <v>-5.741776328191382</v>
       </c>
       <c r="G89">
-        <v>-31.59930564228831</v>
+        <v>-18.26946520514197</v>
       </c>
     </row>
     <row r="90" spans="1:7">
@@ -2450,13 +2450,13 @@
         <v>-7.426494995330518</v>
       </c>
       <c r="E90">
-        <v>-56.05473490179546</v>
+        <v>-41.2178215377876</v>
       </c>
       <c r="F90">
-        <v>-9.652260599035593</v>
+        <v>-5.758455127039833</v>
       </c>
       <c r="G90">
-        <v>-31.76576649309395</v>
+        <v>-18.66526740872616</v>
       </c>
     </row>
     <row r="91" spans="1:7">
@@ -2473,13 +2473,13 @@
         <v>-7.179881342340721</v>
       </c>
       <c r="E91">
-        <v>-56.03652817204762</v>
+        <v>-40.51142714156811</v>
       </c>
       <c r="F91">
-        <v>-9.62220997725337</v>
+        <v>-5.95776689205676</v>
       </c>
       <c r="G91">
-        <v>-31.6372312519862</v>
+        <v>-18.29433898905129</v>
       </c>
     </row>
     <row r="92" spans="1:7">
@@ -2496,13 +2496,13 @@
         <v>-6.913795476050042</v>
       </c>
       <c r="E92">
-        <v>-56.64216968218896</v>
+        <v>-43.53943204306296</v>
       </c>
       <c r="F92">
-        <v>-9.818668894026871</v>
+        <v>-5.555726516510345</v>
       </c>
       <c r="G92">
-        <v>-31.98974972791719</v>
+        <v>-18.50680980176171</v>
       </c>
     </row>
     <row r="93" spans="1:7">
@@ -2519,13 +2519,13 @@
         <v>-6.626711871087789</v>
       </c>
       <c r="E93">
-        <v>-57.03512235361205</v>
+        <v>-44.11557620563683</v>
       </c>
       <c r="F93">
-        <v>-9.705896561163499</v>
+        <v>-6.178378709783391</v>
       </c>
       <c r="G93">
-        <v>-31.80280404895093</v>
+        <v>-19.87204402142899</v>
       </c>
     </row>
     <row r="94" spans="1:7">
@@ -2542,13 +2542,13 @@
         <v>-6.315493543137391</v>
       </c>
       <c r="E94">
-        <v>-57.37376163990563</v>
+        <v>-45.12112159480304</v>
       </c>
       <c r="F94">
-        <v>-9.830463147905627</v>
+        <v>-5.356173236341313</v>
       </c>
       <c r="G94">
-        <v>-31.49577826218422</v>
+        <v>-19.28041973865137</v>
       </c>
     </row>
     <row r="95" spans="1:7">
@@ -2565,13 +2565,13 @@
         <v>-5.987166016731233</v>
       </c>
       <c r="E95">
-        <v>-58.34566725990585</v>
+        <v>-47.4306342817669</v>
       </c>
       <c r="F95">
-        <v>-9.580580089670409</v>
+        <v>-6.09785241102752</v>
       </c>
       <c r="G95">
-        <v>-31.552103056353</v>
+        <v>-18.53036598854639</v>
       </c>
     </row>
     <row r="96" spans="1:7">
@@ -2588,13 +2588,13 @@
         <v>-5.641934369667061</v>
       </c>
       <c r="E96">
-        <v>-58.5736730958958</v>
+        <v>-48.17744078003085</v>
       </c>
       <c r="F96">
-        <v>-9.662488765727218</v>
+        <v>-5.802220840013002</v>
       </c>
       <c r="G96">
-        <v>-31.58227371312515</v>
+        <v>-19.38658396827749</v>
       </c>
     </row>
     <row r="97" spans="1:7">
@@ -2611,13 +2611,13 @@
         <v>-5.283180917189182</v>
       </c>
       <c r="E97">
-        <v>-59.44258649942107</v>
+        <v>-48.21036957877762</v>
       </c>
       <c r="F97">
-        <v>-9.617043334667487</v>
+        <v>-6.103293232700013</v>
       </c>
       <c r="G97">
-        <v>-31.90239436277244</v>
+        <v>-19.51237807767872</v>
       </c>
     </row>
     <row r="98" spans="1:7">
@@ -2634,13 +2634,13 @@
         <v>-4.908951671359746</v>
       </c>
       <c r="E98">
-        <v>-59.51542077718269</v>
+        <v>-49.76291387180433</v>
       </c>
       <c r="F98">
-        <v>-9.699729412365539</v>
+        <v>-6.512526404587875</v>
       </c>
       <c r="G98">
-        <v>-31.82334846693126</v>
+        <v>-19.47623023093541</v>
       </c>
     </row>
     <row r="99" spans="1:7">
@@ -2657,13 +2657,13 @@
         <v>-4.524018068965587</v>
       </c>
       <c r="E99">
-        <v>-60.85457601619771</v>
+        <v>-51.56706470917121</v>
       </c>
       <c r="F99">
-        <v>-9.780413685786474</v>
+        <v>-5.943656072350195</v>
       </c>
       <c r="G99">
-        <v>-32.05389816883164</v>
+        <v>-18.56827007969828</v>
       </c>
     </row>
     <row r="100" spans="1:7">
@@ -2680,13 +2680,13 @@
         <v>-4.128273203778586</v>
       </c>
       <c r="E100">
-        <v>-60.62764682490308</v>
+        <v>-52.32888309877059</v>
       </c>
       <c r="F100">
-        <v>-9.720294625530476</v>
+        <v>-5.572048981527821</v>
       </c>
       <c r="G100">
-        <v>-31.99313641600386</v>
+        <v>-18.33300781622274</v>
       </c>
     </row>
     <row r="101" spans="1:7">
@@ -2703,13 +2703,13 @@
         <v>-3.737967201579468</v>
       </c>
       <c r="E101">
-        <v>-61.69277504476595</v>
+        <v>-53.67274285622032</v>
       </c>
       <c r="F101">
-        <v>-9.70603157209279</v>
+        <v>-5.704704940122776</v>
       </c>
       <c r="G101">
-        <v>-32.33781552009785</v>
+        <v>-19.87277565199317</v>
       </c>
     </row>
     <row r="102" spans="1:7">
@@ -2726,13 +2726,13 @@
         <v>-3.335224792774431</v>
       </c>
       <c r="E102">
-        <v>-62.45020194669639</v>
+        <v>-54.67258010389985</v>
       </c>
       <c r="F102">
-        <v>-9.524897583573276</v>
+        <v>-5.529667427524746</v>
       </c>
       <c r="G102">
-        <v>-31.9199882570409</v>
+        <v>-19.49863103732689</v>
       </c>
     </row>
   </sheetData>
